--- a/data/trans_orig/RUIDO_1-Edad-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1-Edad-trans_orig.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2477</t>
+          <t>2187</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2348</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3731</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>1634</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>401</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>4517</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>418</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5179</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>3465</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4542</t>
+          <t>5069</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2039</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>2214</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>2587</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4180</t>
+          <t>4805</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6865</t>
+          <t>6718</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1684,12 +1684,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>2493</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8684</t>
+          <t>8717</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>896</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5718</t>
+          <t>5418</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1782,12 +1782,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>512</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2239</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7384</t>
+          <t>7577</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19129</t>
+          <t>18800</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26191</t>
+          <t>26422</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14830</t>
+          <t>15064</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21273</t>
+          <t>21320</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>36454</t>
+          <t>36296</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46052</t>
+          <t>45955</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,84%</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6892</t>
+          <t>6551</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5964</t>
+          <t>6662</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4139</t>
+          <t>4331</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3601</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>4867</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8951</t>
+          <t>8448</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>8723</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6070</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>2321</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>5959</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2387</t>
+          <t>3155</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>478</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4788</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>6255</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11574</t>
+          <t>11900</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4971</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>15270</t>
+          <t>14604</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -3107,12 +3107,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6304</t>
+          <t>5911</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15024</t>
+          <t>14681</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11985</t>
+          <t>11729</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11686</t>
+          <t>11432</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23094</t>
+          <t>23854</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,83%</t>
         </is>
       </c>
     </row>
@@ -3220,12 +3220,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>51822</t>
+          <t>52929</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>63460</t>
+          <t>63537</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>70943</t>
+          <t>71422</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>85395</t>
+          <t>84680</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>128640</t>
+          <t>128719</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>145278</t>
+          <t>146148</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,76%</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2154</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7149</t>
+          <t>7573</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>431</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8149</t>
+          <t>7820</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t>3994</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>4145</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5545</t>
+          <t>6211</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>5756</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>6473</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>950</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>8057</t>
+          <t>8584</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -4128,12 +4128,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>707</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6849</t>
+          <t>6320</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4143,12 +4143,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>16405</t>
+          <t>14777</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4562</t>
+          <t>4560</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>18422</t>
+          <t>17989</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2903</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>4283</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>5579</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -4354,12 +4354,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>2373</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>10826</t>
+          <t>10731</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>18243</t>
+          <t>17546</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>8792</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>24418</t>
+          <t>24671</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>8687</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>19760</t>
+          <t>19725</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>5980</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>17065</t>
+          <t>16617</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>17103</t>
+          <t>17263</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>32933</t>
+          <t>33559</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,6%</t>
         </is>
       </c>
     </row>
@@ -4580,12 +4580,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>51086</t>
+          <t>51165</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>66433</t>
+          <t>65875</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>73704</t>
+          <t>73724</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>93590</t>
+          <t>92579</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>129297</t>
+          <t>129167</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>154583</t>
+          <t>153899</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,11%</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>4259</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>3504</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>4623</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>5537</t>
+          <t>5446</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2540</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>3753</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>4742</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6184</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>6253</t>
+          <t>6925</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -5488,12 +5488,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>706</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>9492</t>
+          <t>9922</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>901</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10093</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>2592</t>
+          <t>2523</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>14352</t>
+          <t>14187</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -5601,12 +5601,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>466</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>5520</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>453</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>9581</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5651,12 +5651,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1609</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>8955</t>
+          <t>9735</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5686,12 +5686,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -5714,12 +5714,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2857</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>12976</t>
+          <t>12983</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5729,12 +5729,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1557</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>8943</t>
+          <t>8990</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5764,12 +5764,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>6002</t>
+          <t>6363</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>18447</t>
+          <t>18182</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5799,12 +5799,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -5827,12 +5827,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>19169</t>
+          <t>20022</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>15652</t>
+          <t>15932</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>39205</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5877,12 +5877,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>23905</t>
+          <t>24287</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>51852</t>
+          <t>51865</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>105041</t>
+          <t>105683</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>129077</t>
+          <t>128615</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>93182</t>
+          <t>93350</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>116913</t>
+          <t>116188</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>206356</t>
+          <t>205871</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>242442</t>
+          <t>243707</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6025,12 +6025,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,94%</t>
         </is>
       </c>
     </row>
@@ -6170,12 +6170,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>428</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5694</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6220,12 +6220,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>2531</t>
+          <t>2396</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>13037</t>
+          <t>12603</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6255,12 +6255,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>4995</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6318,12 +6318,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6098</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6353,12 +6353,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>8799</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6368,12 +6368,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -6436,7 +6436,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>5045</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>2524</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5160</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>996</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>12106</t>
+          <t>11031</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>2433</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>12825</t>
+          <t>12040</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6707,12 +6707,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>8622</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>950</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>9668</t>
+          <t>9063</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>3710</t>
+          <t>3578</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>13972</t>
+          <t>13719</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -6848,12 +6848,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>3819</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>15845</t>
+          <t>15478</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6863,12 +6863,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>6152</t>
+          <t>5707</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>23595</t>
+          <t>21840</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>11612</t>
+          <t>11565</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>29946</t>
+          <t>29896</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>8381</t>
+          <t>8930</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6976,12 +6976,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>9683</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7011,12 +7011,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>4378</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>14229</t>
+          <t>14254</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -7074,12 +7074,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>10164</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>23920</t>
+          <t>23670</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7089,12 +7089,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7109,12 +7109,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>15630</t>
+          <t>16138</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>34584</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7124,12 +7124,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>29390</t>
+          <t>28919</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>52138</t>
+          <t>51265</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -7187,12 +7187,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>28156</t>
+          <t>27754</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>48959</t>
+          <t>49269</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7202,12 +7202,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>33605</t>
+          <t>32627</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>63226</t>
+          <t>60677</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7237,12 +7237,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7257,12 +7257,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>66814</t>
+          <t>66152</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>100240</t>
+          <t>100004</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -7300,12 +7300,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>240776</t>
+          <t>242664</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>274374</t>
+          <t>275054</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7315,12 +7315,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7335,12 +7335,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>268712</t>
+          <t>268513</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>303539</t>
+          <t>303444</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7350,12 +7350,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>523082</t>
+          <t>519201</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>570088</t>
+          <t>569331</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,33%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/RUIDO_1-Edad-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>461</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2187</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,3%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>382</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>382</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -833,82 +833,82 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>644</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2616</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>12,48%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>766</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>3724</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>14,21%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>644</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3700</t>
+          <t>3462</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -1059,82 +1059,82 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>323</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1636</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,81%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1634</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>6,23%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>323</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -1285,72 +1285,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1747</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>4517</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>15,08%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1665</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>360</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4586</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>1665</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>382</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>626</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1413,12 +1413,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3465</t>
+          <t>2671</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>782</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>4061</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5069</t>
+          <t>4531</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>298</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1526,12 +1526,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>1792</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>326</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2214</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>624</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2587</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -1624,72 +1624,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3097</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>5652</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>14,78%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6,46%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>26,97%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>854</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4805</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>16,05%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>659</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6718</t>
+          <t>3239</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1699,32 +1699,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>4712</t>
+          <t>3756</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2493</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8717</t>
+          <t>6604</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -1737,72 +1737,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>461</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3758</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,3%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>17,93%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2542</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>896</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5418</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>8,49%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>18,09%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1748</t>
+          <t>2386</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>798</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4235</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1812,32 +1812,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4290</t>
+          <t>3916</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2239</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7577</t>
+          <t>7017</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -1850,72 +1850,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>14438</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>11520</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>17031</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>68,9%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>54,97%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>81,27%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>23177</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>18800</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>26422</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>77,39%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>62,78%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>88,23%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>20885</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15064</t>
+          <t>17421</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21320</t>
+          <t>23783</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1925,32 +1925,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>41597</t>
+          <t>35323</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>36296</t>
+          <t>30780</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>45955</t>
+          <t>39067</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,32%</t>
         </is>
       </c>
     </row>
@@ -1963,74 +1963,74 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>20956</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>20956</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>20956</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>29947</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>29947</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>29947</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>27085</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>27085</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>27085</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>26208</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>26208</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>26208</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>110</t>
@@ -2038,17 +2038,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>56154</t>
+          <t>48041</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>56154</t>
+          <t>48041</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>56154</t>
+          <t>48041</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2080,82 +2080,82 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5839</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,92%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1922</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6551</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>6,7%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6662</t>
+          <t>5658</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>569</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2208,12 +2208,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>2736</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>860</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3617</t>
+          <t>4268</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4867</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -2532,82 +2532,82 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>6455</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>7,65%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>2529</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>8448</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>8,63%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8723</t>
+          <t>6622</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -2758,47 +2758,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1849</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>1546</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5292</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>7,1%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>1564</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2321</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2833,32 +2833,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>363</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5959</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -2871,47 +2871,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1779</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>1223</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>3860</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>5,18%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3586</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>353</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -2984,72 +2984,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>4553</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>8637</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>5,39%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>10,23%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>2646</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>1041</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>6255</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>8,39%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5998</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2992</t>
+          <t>845</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11900</t>
+          <t>5845</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3059,32 +3059,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>8644</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>14604</t>
+          <t>12632</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -3097,72 +3097,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>6286</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>3359</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>10776</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>7,45%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>3,98%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>12,77%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>9982</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>5911</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>14681</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>13,39%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>7,93%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>19,69%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>6958</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>6382</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11729</t>
+          <t>14873</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3172,32 +3172,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>16941</t>
+          <t>16258</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11432</t>
+          <t>11161</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23854</t>
+          <t>22389</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,72%</t>
         </is>
       </c>
     </row>
@@ -3210,72 +3210,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>68480</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>61933</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>73135</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>81,15%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>73,39%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>86,66%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>58355</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>52929</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>63537</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>78,25%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>70,97%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>85,2%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>78805</t>
+          <t>51860</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>71422</t>
+          <t>46224</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>84680</t>
+          <t>56619</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3285,32 +3285,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>137160</t>
+          <t>120340</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>128719</t>
+          <t>112263</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>146148</t>
+          <t>127690</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>83,96%</t>
         </is>
       </c>
     </row>
@@ -3323,74 +3323,74 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>84390</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>84390</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>84390</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>74574</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>74574</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>74574</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>67700</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>67700</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>67700</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="P27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>97845</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>97845</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>97845</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>274</t>
@@ -3398,17 +3398,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>172419</t>
+          <t>152089</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>172419</t>
+          <t>152089</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>172419</t>
+          <t>152089</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3440,47 +3440,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>7570</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>6,69%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>2118</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>366</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7573</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3515,32 +3515,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2526</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>367</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7820</t>
+          <t>6727</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -3666,82 +3666,82 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>961</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>5448</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>4,82%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>4679</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>3,97%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>961</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>5375</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>962</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3994</t>
+          <t>4874</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>705</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4145</t>
+          <t>4268</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1748</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6211</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -4020,12 +4020,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>5756</t>
+          <t>6720</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>5278</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4080,22 +4080,22 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>3547</t>
+          <t>3647</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>932</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>8584</t>
+          <t>9045</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -4118,72 +4118,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>5394</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>11036</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>4,77%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>9,76%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>2594</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>707</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>6320</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>7,5%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>6810</t>
+          <t>2775</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>817</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>14777</t>
+          <t>6923</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4193,32 +4193,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>9404</t>
+          <t>8170</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>17989</t>
+          <t>15895</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>926</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4246,12 +4246,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>4512</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>647</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4283</t>
+          <t>3199</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>1608</t>
+          <t>1573</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>5579</t>
+          <t>4734</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -4344,72 +4344,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>9289</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>4323</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>17200</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>8,21%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>3,82%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>15,2%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>5544</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>2373</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>10731</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>6,57%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>12,73%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>9469</t>
+          <t>5303</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>4737</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>17546</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4419,32 +4419,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>15013</t>
+          <t>14591</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>8792</t>
+          <t>8565</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>24671</t>
+          <t>24371</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -4457,72 +4457,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>10831</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>6213</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>17211</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>9,57%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>5,49%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>15,21%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>13366</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>8687</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>19725</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>15,85%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>10,3%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>23,39%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>10833</t>
+          <t>14157</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>9117</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>16617</t>
+          <t>20405</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4532,32 +4532,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>24199</t>
+          <t>24988</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>17263</t>
+          <t>17559</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>33559</t>
+          <t>34257</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>17,36%</t>
         </is>
       </c>
     </row>
@@ -4570,72 +4570,72 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>80884</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>70526</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>90053</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>71,5%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>62,34%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>79,6%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>59226</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>51165</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>65875</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>70,24%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>60,68%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>78,13%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>83954</t>
+          <t>58527</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>73724</t>
+          <t>51209</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>92579</t>
+          <t>65202</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4645,32 +4645,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>143179</t>
+          <t>139411</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>129167</t>
+          <t>128306</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>153899</t>
+          <t>151191</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>76,61%</t>
         </is>
       </c>
     </row>
@@ -4683,74 +4683,74 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>113132</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>113132</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>113132</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>84320</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>84320</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>84320</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>84213</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>84213</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>84213</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="P39" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>117881</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>117881</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>117881</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
           <t>251</t>
@@ -4758,17 +4758,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>202200</t>
+          <t>197346</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>202200</t>
+          <t>197346</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>202200</t>
+          <t>197346</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4800,72 +4800,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>716</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>4259</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>751</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3793</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>751</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>4147</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>891</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>4391</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>751</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4256</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>1569</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>5446</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -5139,72 +5139,72 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>2411</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>2115</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
         <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>342</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>1726</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -5257,7 +5257,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>953</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>777</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>4771</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>1699</t>
+          <t>1730</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6184</t>
+          <t>5970</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -5365,82 +5365,82 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>6692</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="M45" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="P45" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="Q45" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>1833</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>6030</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
@@ -5450,12 +5450,12 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>6925</t>
+          <t>6648</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -5483,32 +5483,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>3145</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>883</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>9922</t>
+          <t>9318</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5518,32 +5518,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>3502</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>785</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>10093</t>
+          <t>9095</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5553,32 +5553,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>6647</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>14187</t>
+          <t>14920</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -5596,32 +5596,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>1780</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>367</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>6738</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5631,32 +5631,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>2273</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>543</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>8309</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5666,32 +5666,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>4053</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>9735</t>
+          <t>8273</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -5704,72 +5704,72 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>4182</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>9263</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>6,64%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>6886</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>2952</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>12983</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>4,83%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>9,1%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>3766</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>8990</t>
+          <t>12934</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5779,32 +5779,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>10997</t>
+          <t>11431</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>6363</t>
+          <t>6660</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>18182</t>
+          <t>18462</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -5817,72 +5817,72 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>23460</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>15836</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>36854</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>16,82%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>11,35%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>26,42%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>12398</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>6309</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>20022</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>8,69%</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>14,03%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>23566</t>
+          <t>13069</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>15932</t>
+          <t>8599</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>39205</t>
+          <t>19308</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5892,32 +5892,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>35964</t>
+          <t>36529</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>24287</t>
+          <t>27400</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>51865</t>
+          <t>49008</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -5935,32 +5935,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>115919</t>
+          <t>102809</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>105683</t>
+          <t>89979</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>128615</t>
+          <t>112170</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5970,32 +5970,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>107115</t>
+          <t>93409</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>93350</t>
+          <t>85519</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>116188</t>
+          <t>100912</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6005,32 +6005,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>223034</t>
+          <t>196218</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>205871</t>
+          <t>181592</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>243707</t>
+          <t>208055</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>79,64%</t>
         </is>
       </c>
     </row>
@@ -6043,74 +6043,74 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>139486</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>139486</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>139486</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>142702</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>142702</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>142702</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>121771</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>121771</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>121771</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="O51" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
+      <c r="P51" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>144216</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>144216</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>144216</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
           <t>344</t>
@@ -6118,17 +6118,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>286918</t>
+          <t>261257</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>286918</t>
+          <t>261257</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>286918</t>
+          <t>261257</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6160,72 +6160,72 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>3815</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>984</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>9011</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>1599</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>428</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>5694</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>368</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6235,22 +6235,22 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>5626</t>
+          <t>5314</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>2396</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>12603</t>
+          <t>10821</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -6273,72 +6273,72 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>566</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>5978</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>1538</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>4995</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>6098</t>
+          <t>5525</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6348,22 +6348,22 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1438</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>8799</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -6386,82 +6386,82 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>961</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>4030</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="M54" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
+      <c r="P54" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="Q54" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>4863</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P54" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="Q54" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>961</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>5045</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>323</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>342</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
@@ -6549,49 +6549,49 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>2366</t>
+        </is>
+      </c>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
           <t>0,1%</t>
         </is>
       </c>
-      <c r="O55" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P55" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="Q55" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R55" s="2" t="inlineStr">
-        <is>
-          <t>796</t>
-        </is>
-      </c>
-      <c r="S55" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T55" s="2" t="inlineStr">
-        <is>
-          <t>2465</t>
-        </is>
-      </c>
-      <c r="U55" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -6612,72 +6612,72 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>3862</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>9542</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>1546</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>5160</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>11031</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6687,32 +6687,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>2227</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>12040</t>
+          <t>11552</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -6725,72 +6725,72 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>3780</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>966</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>9340</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>3408</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>1297</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>8622</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>3398</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>1181</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>7611</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
         <is>
           <t>0,39%</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>3720</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>950</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>9063</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="O57" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6800,32 +6800,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>7128</t>
+          <t>7178</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>3578</t>
+          <t>3882</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>13719</t>
+          <t>13503</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -6838,72 +6838,72 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>9780</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>5022</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>17711</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>8069</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>3819</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>15478</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>11406</t>
+          <t>8610</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>5707</t>
+          <t>4474</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>21840</t>
+          <t>15867</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6913,32 +6913,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>19475</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>11565</t>
+          <t>11686</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>29896</t>
+          <t>28049</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -6951,72 +6951,72 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>3502</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>1257</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>9161</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>4080</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>1876</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>8930</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1693</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>8372</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7026,17 +7026,17 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>4378</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>14254</t>
+          <t>13273</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -7064,72 +7064,72 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>21121</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>13849</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>29605</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>3,87%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>8,27%</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>15930</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>10164</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>23670</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>7,14%</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>23435</t>
+          <t>15649</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>16138</t>
+          <t>10078</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>34584</t>
+          <t>22903</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7139,32 +7139,32 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>39365</t>
+          <t>36769</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>28919</t>
+          <t>27282</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>51265</t>
+          <t>47878</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -7177,72 +7177,72 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>42107</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>32148</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>59117</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>11,76%</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>8,98%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>16,51%</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>38289</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>27754</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>49269</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>11,55%</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>8,37%</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>14,86%</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>43105</t>
+          <t>39583</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>32627</t>
+          <t>30456</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>60677</t>
+          <t>49753</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7252,32 +7252,32 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>81394</t>
+          <t>81691</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>66152</t>
+          <t>68681</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>100004</t>
+          <t>99951</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -7290,72 +7290,72 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>266611</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>249873</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>282316</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>74,48%</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>69,8%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>78,87%</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
           <t>351</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>256677</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>242664</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>275054</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>77,42%</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>73,19%</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>82,96%</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>288294</t>
+          <t>224681</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>268513</t>
+          <t>211785</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>303444</t>
+          <t>236506</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7365,32 +7365,32 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>544970</t>
+          <t>491292</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>519201</t>
+          <t>469918</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>569331</t>
+          <t>509658</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>77,37%</t>
         </is>
       </c>
     </row>
@@ -7403,74 +7403,74 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
           <t>468</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>331543</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>331543</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>331543</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>300769</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>300769</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>300769</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="O63" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
+      <c r="P63" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>386149</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>386149</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>386149</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P63" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
           <t>979</t>
@@ -7478,17 +7478,17 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>717691</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>717691</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>717691</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
